--- a/Excel/Terminologies.xlsx
+++ b/Excel/Terminologies.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ANALYST\AI NIXA\Excel-PowerBI-training-resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{786E7336-5534-4796-AD7B-62B61453988F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F465796C-B286-4334-8A84-9A3D5BDF5A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{28C6DB65-C130-4D7D-8A07-4DC77FB16E85}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{28C6DB65-C130-4D7D-8A07-4DC77FB16E85}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="100">
   <si>
     <t>Term</t>
   </si>
@@ -147,6 +148,198 @@
   </si>
   <si>
     <t>Displays geographical data on an interactive map to identify patterns and trends by location.</t>
+  </si>
+  <si>
+    <t>one to one</t>
+  </si>
+  <si>
+    <t>Only one record in Table A --&gt; Only one record in Table B</t>
+  </si>
+  <si>
+    <t>Predict the future value by analysing the historical data</t>
+  </si>
+  <si>
+    <t>one to many</t>
+  </si>
+  <si>
+    <t>Only one record in Table A --&gt; Many records in Table B</t>
+  </si>
+  <si>
+    <t>how two tables are connected through common column (field)</t>
+  </si>
+  <si>
+    <t>many to one</t>
+  </si>
+  <si>
+    <t>Many records in Table A --&gt; Only one record in Table B</t>
+  </si>
+  <si>
+    <t>ETL</t>
+  </si>
+  <si>
+    <t>EXTRACT, TRANSFORM, LOAD</t>
+  </si>
+  <si>
+    <t>many to many</t>
+  </si>
+  <si>
+    <t>Many records in Table A --&gt; Many records in Table B</t>
+  </si>
+  <si>
+    <t>ELT</t>
+  </si>
+  <si>
+    <t>EXTRACT, LOAD, TRANSFORM</t>
+  </si>
+  <si>
+    <t>Visualization</t>
+  </si>
+  <si>
+    <t>Visuals of Analysis in chart</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>The finnal insight which have all analysis visuals</t>
+  </si>
+  <si>
+    <t>SOUTH</t>
+  </si>
+  <si>
+    <t>55%, 42%</t>
+  </si>
+  <si>
+    <t>85%, 20%</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>Customer Relationship Management</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>windspeed</t>
+  </si>
+  <si>
+    <t>humid</t>
+  </si>
+  <si>
+    <t>Temp</t>
+  </si>
+  <si>
+    <t>Rain</t>
+  </si>
+  <si>
+    <t>sept1, 2026</t>
+  </si>
+  <si>
+    <t>2km/hr</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Emp id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passport no </t>
+  </si>
+  <si>
+    <t>sss</t>
+  </si>
+  <si>
+    <t>dep id</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+  <si>
+    <t>emp id</t>
+  </si>
+  <si>
+    <t>d1</t>
+  </si>
+  <si>
+    <t>finance</t>
+  </si>
+  <si>
+    <t>as</t>
+  </si>
+  <si>
+    <t xml:space="preserve">many to many </t>
+  </si>
+  <si>
+    <t>st id</t>
+  </si>
+  <si>
+    <t>course id</t>
+  </si>
+  <si>
+    <t>s1</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>c1</t>
+  </si>
+  <si>
+    <t>SQL</t>
+  </si>
+  <si>
+    <t>s2</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>c2</t>
+  </si>
+  <si>
+    <t>BI</t>
+  </si>
+  <si>
+    <t>s3</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>c3</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>ST ID</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>C3</t>
   </si>
 </sst>
 </file>
@@ -170,12 +363,36 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -190,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -201,6 +418,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -538,7 +762,7 @@
   <dimension ref="A1:B18"/>
   <sheetFormatPr defaultColWidth="80.33203125" defaultRowHeight="48" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="42.44140625" customWidth="1"/>
+    <col min="1" max="1" width="80.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.3">
@@ -687,5 +911,394 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14BFE666-9E1E-4F86-9A08-F1B48E941303}">
+  <dimension ref="B1:K57"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="9" max="9" width="25.44140625" customWidth="1"/>
+    <col min="10" max="10" width="19.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="J1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="E9">
+        <v>2024</v>
+      </c>
+      <c r="F9">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="10" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="I13" t="s">
+        <v>58</v>
+      </c>
+      <c r="J13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19">
+        <v>10</v>
+      </c>
+      <c r="E19">
+        <v>26</v>
+      </c>
+      <c r="F19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D32">
+        <v>101</v>
+      </c>
+      <c r="E32" t="s">
+        <v>71</v>
+      </c>
+      <c r="H32">
+        <v>101</v>
+      </c>
+      <c r="I32">
+        <v>109876</v>
+      </c>
+    </row>
+    <row r="36" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C36" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D37" t="s">
+        <v>75</v>
+      </c>
+      <c r="E37" t="s">
+        <v>76</v>
+      </c>
+      <c r="H37">
+        <v>101</v>
+      </c>
+      <c r="I37" t="s">
+        <v>71</v>
+      </c>
+      <c r="J37" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="H38">
+        <v>102</v>
+      </c>
+      <c r="I38" t="s">
+        <v>77</v>
+      </c>
+      <c r="J38" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C41" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G41" s="6"/>
+      <c r="H41" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D42">
+        <v>101</v>
+      </c>
+      <c r="E42" t="s">
+        <v>71</v>
+      </c>
+      <c r="F42" t="s">
+        <v>75</v>
+      </c>
+      <c r="H42" t="s">
+        <v>75</v>
+      </c>
+      <c r="I42" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D43">
+        <v>102</v>
+      </c>
+      <c r="E43" t="s">
+        <v>77</v>
+      </c>
+      <c r="F43" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C46" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D47" t="s">
+        <v>81</v>
+      </c>
+      <c r="E47" t="s">
+        <v>82</v>
+      </c>
+      <c r="H47" t="s">
+        <v>83</v>
+      </c>
+      <c r="I47" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="48" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D48" t="s">
+        <v>85</v>
+      </c>
+      <c r="E48" t="s">
+        <v>86</v>
+      </c>
+      <c r="H48" t="s">
+        <v>87</v>
+      </c>
+      <c r="I48" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D49" t="s">
+        <v>89</v>
+      </c>
+      <c r="E49" t="s">
+        <v>90</v>
+      </c>
+      <c r="H49" t="s">
+        <v>91</v>
+      </c>
+      <c r="I49" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="53" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="F53" t="s">
+        <v>93</v>
+      </c>
+      <c r="G53" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="54" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="F54" t="s">
+        <v>95</v>
+      </c>
+      <c r="G54" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="55" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="F55" t="s">
+        <v>95</v>
+      </c>
+      <c r="G55" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="56" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="F56" t="s">
+        <v>98</v>
+      </c>
+      <c r="G56" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="57" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="F57" t="s">
+        <v>98</v>
+      </c>
+      <c r="G57" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>